--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0112.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0112.xlsx
@@ -23851,7 +23851,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Không phải ta không thích thử ẩm thực các vùng khác, chỉ là mùi vị của món này nghe hơi nặng đối với ta.</t>
+          <t>Không phải tao không thích thử ẩm thực các vùng khác, chỉ là mùi vị của món này nghe hơi nặng đối với tao.</t>
         </is>
       </c>
     </row>
@@ -23981,7 +23981,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Nhưng nếu cậu thắng được ta một ván Peaks of Prestige, ta sẽ thử xem sao.</t>
+          <t>Nhưng nếu cậu thắng được tao một ván Peaks of Prestige, tao sẽ thử xem sao.</t>
         </is>
       </c>
     </row>
@@ -25736,7 +25736,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Đ-Đợi đã. Hết hàng rồi à?! Vậy nghĩa là hôm nay chỉ còn… Kẹo Nhồi Nhét à? Ta chưa ăn bao giờ.</t>
+          <t>Đ-Đợi đã. Hết hàng rồi à?! Vậy nghĩa là hôm nay chỉ còn… Kẹo Nhồi Nhét à? Tao chưa ăn bao giờ.</t>
         </is>
       </c>
     </row>
@@ -26646,7 +26646,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Hay là chỉ có mình ta thôi, {PlayerName}. Cậu thử đi... được không?</t>
+          <t>Hay là chỉ có mình tao thôi, {PlayerName}. Cậu thử đi... được không?</t>
         </is>
       </c>
     </row>
@@ -27816,7 +27816,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Nhưng nếu phải chọn... ta muốn thử hương vị "Lẩu Kim Châu".</t>
+          <t>Nhưng nếu phải chọn... ta muốn thử hương vị "Lẩu Jinzhou".</t>
         </is>
       </c>
     </row>
@@ -28141,7 +28141,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Ta muốn ăn Thạch vị Bánh Quế Hoa Trúc. Đó là món ăn ở đấu trường hồi ta đi Gondola tới Septimont xem giải đấu Gladiator.</t>
+          <t>Tao muốn ăn Thạch vị Bánh Quế Hoa Trúc. Đó là món ăn ở đấu trường hồi tao đi Gondola tới Septimont xem giải đấu Gladiator.</t>
         </is>
       </c>
     </row>
@@ -29636,7 +29636,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Chuyện là, dạo này ta đi lại khó khăn lắm. Mà cậu lại đến đây, nên ta tự hỏi... liệu cậu có thể chụp lại những bức ảnh từ bản in của mấy cái Smartprint Cube không?</t>
+          <t>Chuyện là, dạo này tao đi lại khó khăn lắm. Mà cậu lại đến đây, nên tao tự hỏi... liệu cậu có thể chụp lại những bức ảnh từ bản in của mấy cái Smartprint Cube không?</t>
         </is>
       </c>
     </row>
@@ -30091,7 +30091,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>À, đúng rồi, ta thấy cậu dùng xe máy của Học viện. Vậy thì cầm lấy cái này đi.</t>
+          <t>À, đúng rồi, tao thấy cậu dùng xe máy của Học viện. Vậy thì cầm lấy cái này đi.</t>
         </is>
       </c>
     </row>
